--- a/data/trans_dic/IP07_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP07_R2-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7,5%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4,96%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,6%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3,71%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,72%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 8,68</t>
+          <t>2,38; 10,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,37</t>
+          <t>1,5; 9,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 10,55</t>
+          <t>0,91; 7,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 43,84</t>
+          <t>2,93; 15,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 10,96</t>
+          <t>2,13; 9,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 9,46</t>
+          <t>0,7; 6,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,92</t>
+          <t>0,9; 9,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 16,4</t>
+          <t>0,74; 12,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,49</t>
+          <t>2,97; 8,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,19</t>
+          <t>1,68; 6,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 7,14</t>
+          <t>1,22; 7,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 23,03</t>
+          <t>2,74; 10,7</t>
         </is>
       </c>
     </row>
@@ -789,49 +789,49 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,56%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,81%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,16%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2,53%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>2,7%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,64</t>
+          <t>2,21; 4,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,37</t>
+          <t>1,66; 4,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,48</t>
+          <t>1,41; 3,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,09</t>
+          <t>0,84; 2,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,89</t>
+          <t>0,73; 2,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,04</t>
+          <t>1,61; 4,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,75</t>
+          <t>1,23; 3,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,03</t>
+          <t>1,5; 4,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,51</t>
+          <t>1,77; 3,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 3,68</t>
+          <t>1,96; 3,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,13</t>
+          <t>1,56; 3,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,96</t>
+          <t>1,41; 3,18</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>1,26; 5,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,28</t>
+          <t>0,38; 4,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,32; 3,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,72</t>
+          <t>1,27; 7,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,61</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,34</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,1</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 6,63</t>
+          <t>0,54; 5,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,18</t>
+          <t>0,75; 2,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,55</t>
+          <t>0,43; 2,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,12</t>
+          <t>0,29; 1,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,49</t>
+          <t>1,17; 4,81</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,71%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,34%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,91%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,74</t>
+          <t>2,6; 4,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,42</t>
+          <t>1,66; 3,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,05</t>
+          <t>1,29; 3,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,55</t>
+          <t>1,54; 3,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,72</t>
+          <t>1,01; 2,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,53</t>
+          <t>1,53; 3,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,08</t>
+          <t>1,21; 2,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,62</t>
+          <t>1,6; 3,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,33</t>
+          <t>2,02; 3,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,15</t>
+          <t>1,87; 3,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,66</t>
+          <t>1,49; 2,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,33</t>
+          <t>1,86; 3,33</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1373,37 +1373,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4811</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3710</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4257</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>4503</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2397</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2205</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6953</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4811</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3710</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11678</t>
+          <t>6077</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1881; 7891</t>
+          <t>2049; 8877</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>656; 5884</t>
+          <t>1282; 7966</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>531; 6264</t>
+          <t>624; 5437</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>456; 23974</t>
+          <t>1664; 8704</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2054; 9444</t>
+          <t>1940; 9061</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1436; 8070</t>
+          <t>648; 5937</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>633; 5431</t>
+          <t>531; 5905</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1959; 10166</t>
+          <t>347; 5690</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5231; 15031</t>
+          <t>5263; 15340</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2731; 10995</t>
+          <t>2987; 10718</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1792; 9140</t>
+          <t>1567; 8978</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4775; 26873</t>
+          <t>2836; 11078</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16010</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12777</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11375</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7609</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6510</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>12664</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>10121</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11631</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16010</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12777</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11375</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>11609</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20048</t>
+          <t>19218</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3138; 11002</t>
+          <t>10529; 23273</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7519; 19703</t>
+          <t>8175; 19764</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5892; 16322</t>
+          <t>6838; 18253</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6575; 18831</t>
+          <t>3979; 13908</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10929; 23244</t>
+          <t>3038; 11818</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8137; 19846</t>
+          <t>7272; 19066</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6777; 18247</t>
+          <t>5746; 16194</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4543; 15672</t>
+          <t>6471; 18429</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15883; 31266</t>
+          <t>15746; 31051</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18190; 34645</t>
+          <t>18506; 33715</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14510; 29933</t>
+          <t>14890; 29946</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13583; 28951</t>
+          <t>12785; 28878</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4594</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2240</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1558</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1073</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2560</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4594</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2240</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2103</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>7976</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3173</t>
+          <t>1987; 9215</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5439</t>
+          <t>647; 7137</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3434</t>
+          <t>594; 5950</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>804; 7064</t>
+          <t>2145; 12147</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1978; 8840</t>
+          <t>0; 3499</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>639; 5754</t>
+          <t>0; 4823</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>595; 5790</t>
+          <t>0; 3360</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2280; 12163</t>
+          <t>805; 7967</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2539; 10551</t>
+          <t>2500; 9905</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1296; 8624</t>
+          <t>1445; 9219</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1145; 7586</t>
+          <t>1035; 6984</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3748; 14937</t>
+          <t>3726; 15322</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>25414</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18726</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15499</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17131</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>11645</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>16619</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>13398</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>21144</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>25414</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>18726</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15499</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18669</t>
+          <t>16140</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39813</t>
+          <t>33271</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7265; 18649</t>
+          <t>18677; 33624</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10563; 24280</t>
+          <t>12455; 26109</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8737; 21336</t>
+          <t>9584; 23187</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12859; 43533</t>
+          <t>10764; 25332</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18605; 33960</t>
+          <t>6868; 18628</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12934; 26451</t>
+          <t>10857; 24748</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9417; 22821</t>
+          <t>8496; 20805</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11965; 27555</t>
+          <t>10067; 24401</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27945; 46639</t>
+          <t>28343; 46736</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26620; 45871</t>
+          <t>27202; 46628</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20921; 38333</t>
+          <t>21541; 37817</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>28183; 61755</t>
+          <t>24787; 44310</t>
         </is>
       </c>
     </row>
